--- a/data/trans_bre/P29A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,19; -10,35</t>
+          <t>-24,29; -11,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -12,56</t>
+          <t>-25,97; -11,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,49; -11,09</t>
+          <t>-24,39; -10,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 0,22</t>
+          <t>-21,57; 1,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -20,76</t>
+          <t>-42,55; -23,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,32; -22,51</t>
+          <t>-42,37; -21,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,23; -19,69</t>
+          <t>-38,81; -18,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 0,69</t>
+          <t>-44,71; 2,88</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,62; -27,08</t>
+          <t>-37,83; -27,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,87; -27,08</t>
+          <t>-37,86; -26,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,35; -14,87</t>
+          <t>-26,29; -14,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,65; -17,39</t>
+          <t>-38,57; -18,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,0; -42,75</t>
+          <t>-56,31; -43,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,62; -44,09</t>
+          <t>-57,63; -43,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,96; -26,24</t>
+          <t>-42,48; -25,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,58; -35,57</t>
+          <t>-66,78; -35,96</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-35,14; -24,5</t>
+          <t>-35,2; -24,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-35,79; -24,55</t>
+          <t>-35,66; -25,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,59; -21,98</t>
+          <t>-32,62; -21,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,43; -19,33</t>
+          <t>-30,1; -19,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -42,48</t>
+          <t>-56,09; -42,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,13; -43,23</t>
+          <t>-57,45; -43,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,81; -35,74</t>
+          <t>-49,71; -35,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,1; -39,26</t>
+          <t>-54,59; -38,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; -26,64</t>
+          <t>-38,57; -26,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,74; -23,53</t>
+          <t>-35,29; -23,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,07; -14,6</t>
+          <t>-26,55; -14,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 10,24</t>
+          <t>-28,2; 13,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,68; -48,51</t>
+          <t>-64,23; -48,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,5; -41,06</t>
+          <t>-55,7; -40,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,43; -25,84</t>
+          <t>-43,18; -26,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,03; 57,16</t>
+          <t>-51,9; 82,58</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,53; -20,91</t>
+          <t>-33,33; -20,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -22,18</t>
+          <t>-34,99; -22,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,51; -26,35</t>
+          <t>-38,89; -25,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,25; -17,48</t>
+          <t>-27,04; -17,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,53; -50,81</t>
+          <t>-69,77; -50,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,28; -46,59</t>
+          <t>-65,57; -46,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,51; -48,23</t>
+          <t>-64,25; -47,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,43; -39,75</t>
+          <t>-54,14; -39,42</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,57; -28,23</t>
+          <t>-41,19; -28,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,04; -26,97</t>
+          <t>-41,36; -27,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -27,17</t>
+          <t>-40,12; -26,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 24,84</t>
+          <t>-34,01; 26,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,4; -72,99</t>
+          <t>-87,59; -73,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,92; -63,94</t>
+          <t>-81,05; -63,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,3; -56,42</t>
+          <t>-74,05; -56,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 51,29</t>
+          <t>-65,14; 52,81</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-36,44; -22,0</t>
+          <t>-35,89; -21,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-34,04; -20,86</t>
+          <t>-34,72; -21,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-33,9; -21,27</t>
+          <t>-34,51; -21,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-33,74; -24,04</t>
+          <t>-33,69; -24,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-92,63; -76,4</t>
+          <t>-92,42; -75,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-90,52; -74,52</t>
+          <t>-90,83; -74,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-85,8; -65,86</t>
+          <t>-86,35; -66,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-86,49; -75,78</t>
+          <t>-86,64; -75,6</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -28,28</t>
+          <t>-32,58; -27,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -27,95</t>
+          <t>-32,8; -28,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,68; -23,9</t>
+          <t>-28,88; -23,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -1,38</t>
+          <t>-24,35; -3,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,35; -52,46</t>
+          <t>-58,29; -52,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -50,79</t>
+          <t>-57,27; -51,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,13; -42,69</t>
+          <t>-49,35; -42,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,25; -2,74</t>
+          <t>-50,72; -7,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P29A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P29A_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,28</t>
+          <t>-9,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-24,19%</t>
+          <t>-23,64%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,29; -11,99</t>
+          <t>-23,73; -10,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,97; -11,71</t>
+          <t>-25,7; -12,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,39; -10,17</t>
+          <t>-24,36; -10,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 1,01</t>
+          <t>-20,3; 0,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,55; -23,74</t>
+          <t>-41,93; -21,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -21,44</t>
+          <t>-42,02; -22,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,81; -18,29</t>
+          <t>-39,16; -18,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 2,88</t>
+          <t>-44,03; 0,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-26,48</t>
+          <t>-21,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-48,73%</t>
+          <t>-41,52%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,83; -27,32</t>
+          <t>-37,39; -27,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,86; -26,57</t>
+          <t>-38,39; -27,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,29; -14,73</t>
+          <t>-26,2; -14,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,57; -18,21</t>
+          <t>-28,33; -14,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,31; -43,36</t>
+          <t>-55,58; -42,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,63; -43,55</t>
+          <t>-58,12; -44,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,48; -25,96</t>
+          <t>-42,33; -25,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,78; -35,96</t>
+          <t>-51,36; -30,43</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-24,75</t>
+          <t>-23,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-47,03%</t>
+          <t>-45,74%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-35,2; -24,43</t>
+          <t>-34,99; -24,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-35,66; -25,17</t>
+          <t>-36,0; -25,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,62; -21,43</t>
+          <t>-32,44; -21,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,1; -19,27</t>
+          <t>-28,08; -18,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,09; -42,09</t>
+          <t>-55,94; -43,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,45; -43,99</t>
+          <t>-57,71; -44,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,71; -35,95</t>
+          <t>-49,8; -35,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,59; -38,98</t>
+          <t>-52,82; -38,62</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-11,95</t>
+          <t>-22,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-30,66%</t>
+          <t>-43,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,57; -26,3</t>
+          <t>-38,93; -26,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,29; -23,8</t>
+          <t>-35,46; -23,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,55; -14,83</t>
+          <t>-25,91; -14,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 13,42</t>
+          <t>-26,64; -17,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,23; -48,7</t>
+          <t>-63,73; -48,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,7; -40,62</t>
+          <t>-56,3; -40,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,18; -26,7</t>
+          <t>-41,94; -26,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 82,58</t>
+          <t>-49,85; -36,96</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-22,47</t>
+          <t>-22,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-47,64%</t>
+          <t>-47,48%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,33; -20,33</t>
+          <t>-32,75; -20,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-34,99; -22,08</t>
+          <t>-34,62; -21,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,89; -25,8</t>
+          <t>-39,14; -26,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,04; -17,65</t>
+          <t>-27,22; -17,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,77; -50,38</t>
+          <t>-69,2; -50,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-65,57; -46,09</t>
+          <t>-65,38; -46,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,25; -47,49</t>
+          <t>-64,67; -48,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -39,42</t>
+          <t>-54,56; -40,34</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,63</t>
+          <t>-32,75</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,89%</t>
+          <t>-63,99%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,19; -28,87</t>
+          <t>-40,73; -28,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,36; -27,14</t>
+          <t>-41,17; -27,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,12; -26,8</t>
+          <t>-39,49; -26,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 26,84</t>
+          <t>-37,4; -27,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,59; -73,59</t>
+          <t>-87,19; -73,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,05; -63,25</t>
+          <t>-81,14; -63,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,05; -56,77</t>
+          <t>-73,61; -55,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 52,81</t>
+          <t>-69,44; -57,75</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-28,81</t>
+          <t>-28,47</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-81,66%</t>
+          <t>-80,67%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -21,45</t>
+          <t>-36,13; -22,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-34,72; -21,19</t>
+          <t>-34,43; -20,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,51; -21,48</t>
+          <t>-34,15; -21,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-33,69; -24,13</t>
+          <t>-33,44; -23,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-92,42; -75,6</t>
+          <t>-92,86; -76,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -74,88</t>
+          <t>-91,32; -74,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-86,35; -66,71</t>
+          <t>-86,19; -65,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-86,64; -75,6</t>
+          <t>-85,51; -73,45</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-17,61</t>
+          <t>-23,37</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-38,49%</t>
+          <t>-48,96%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -27,95</t>
+          <t>-32,84; -28,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,8; -28,13</t>
+          <t>-32,73; -28,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -23,99</t>
+          <t>-28,87; -23,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,35; -3,41</t>
+          <t>-25,36; -20,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,29; -52,1</t>
+          <t>-58,51; -52,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,27; -51,17</t>
+          <t>-56,98; -50,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,35; -42,69</t>
+          <t>-49,33; -42,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,72; -7,52</t>
+          <t>-51,99; -45,27</t>
         </is>
       </c>
     </row>
